--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:50</t>
+          <t>更新时间: 2026-09-13 15:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 15:31</t>
+          <t>更新时间: 2026-09-13 17:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 17:23</t>
+          <t>更新时间: 2026-09-14 09:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 09:38</t>
+          <t>更新时间: 2026-09-14 12:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 12:49</t>
+          <t>更新时间: 2026-09-14 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 13:57</t>
+          <t>更新时间: 2026-09-14 15:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 15:58</t>
+          <t>更新时间: 2026-09-14 17:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 17:43</t>
+          <t>更新时间: 2026-09-15 09:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 09:58</t>
+          <t>更新时间: 2026-09-15 12:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 12:48</t>
+          <t>更新时间: 2026-09-15 13:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 13:58</t>
+          <t>更新时间: 2026-09-15 15:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 15:51</t>
+          <t>更新时间: 2026-09-15 17:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 17:18</t>
+          <t>更新时间: 2026-09-16 09:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 09:47</t>
+          <t>更新时间: 2026-09-16 12:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 12:43</t>
+          <t>更新时间: 2026-09-16 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:49</t>
+          <t>更新时间: 2026-09-16 15:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 15:45</t>
+          <t>更新时间: 2026-09-16 17:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 17:11</t>
+          <t>更新时间: 2026-09-17 09:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:55</t>
+          <t>更新时间: 2026-09-17 15:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 15:47</t>
+          <t>更新时间: 2026-09-17 17:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 17:19</t>
+          <t>更新时间: 2026-09-18 09:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 12:36</t>
+          <t>更新时间: 2026-09-18 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 15:28</t>
+          <t>更新时间: 2026-09-18 16:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 16:54</t>
+          <t>更新时间: 2026-09-19 09:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:40</t>
+          <t>更新时间: 2026-09-19 12:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 12:32</t>
+          <t>更新时间: 2026-09-19 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:36</t>
+          <t>更新时间: 2026-09-19 15:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 15:24</t>
+          <t>更新时间: 2026-09-19 16:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 16:42</t>
+          <t>更新时间: 2026-09-20 09:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 09:43</t>
+          <t>更新时间: 2026-09-20 12:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 12:48</t>
+          <t>更新时间: 2026-09-20 13:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:55</t>
+          <t>更新时间: 2026-09-20 15:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 15:47</t>
+          <t>更新时间: 2026-09-20 17:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 17:10</t>
+          <t>更新时间: 2026-09-21 09:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:38</t>
+          <t>更新时间: 2026-09-21 12:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 12:49</t>
+          <t>更新时间: 2026-09-21 14:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 14:01</t>
+          <t>更新时间: 2026-09-21 16:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 16:01</t>
+          <t>更新时间: 2026-09-21 17:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 17:47</t>
+          <t>更新时间: 2026-09-22 09:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 09:59</t>
+          <t>更新时间: 2026-09-22 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 12:47</t>
+          <t>更新时间: 2026-09-22 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 15:47</t>
+          <t>更新时间: 2026-09-22 17:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 17:11</t>
+          <t>更新时间: 2026-09-23 09:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:59</t>
+          <t>更新时间: 2026-09-23 12:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 12:39</t>
+          <t>更新时间: 2026-09-23 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:42</t>
+          <t>更新时间: 2026-09-23 15:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 15:50</t>
+          <t>更新时间: 2026-09-23 17:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 17:12</t>
+          <t>更新时间: 2026-09-24 09:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 09:51</t>
+          <t>更新时间: 2026-09-24 12:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 12:41</t>
+          <t>更新时间: 2026-09-24 13:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 15:40</t>
+          <t>更新时间: 2026-09-24 17:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 17:10</t>
+          <t>更新时间: 2026-09-25 10:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 10:03</t>
+          <t>更新时间: 2026-09-25 12:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 12:50</t>
+          <t>更新时间: 2026-09-25 13:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:59</t>
+          <t>更新时间: 2026-09-25 15:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 15:57</t>
+          <t>更新时间: 2026-09-25 17:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 17:29</t>
+          <t>更新时间: 2026-09-26 10:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 10:10</t>
+          <t>更新时间: 2026-09-26 12:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 12:50</t>
+          <t>更新时间: 2026-09-26 13:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:59</t>
+          <t>更新时间: 2026-09-26 15:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 15:50</t>
+          <t>更新时间: 2026-09-26 17:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 17:15</t>
+          <t>更新时间: 2026-09-27 09:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:59</t>
+          <t>更新时间: 2026-09-27 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:12</t>
+          <t>更新时间: 2026-09-27 14:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 14:26</t>
+          <t>更新时间: 2026-09-27 16:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 16:20</t>
+          <t>更新时间: 2026-09-27 17:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 17:54</t>
+          <t>更新时间: 2026-09-28 10:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 10:09</t>
+          <t>更新时间: 2026-09-28 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 13:16</t>
+          <t>更新时间: 2026-09-28 14:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:32</t>
+          <t>更新时间: 2026-09-28 16:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 16:47</t>
+          <t>更新时间: 2026-09-28 18:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 18:44</t>
+          <t>更新时间: 2026-09-29 10:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 10:56</t>
+          <t>更新时间: 2026-09-29 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:42</t>
+          <t>更新时间: 2026-09-29 16:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 16:41</t>
+          <t>更新时间: 2026-09-29 18:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 18:31</t>
+          <t>更新时间: 2026-09-30 10:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 10:31</t>
+          <t>更新时间: 2026-09-30 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 13:26</t>
+          <t>更新时间: 2026-09-30 14:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:29</t>
+          <t>更新时间: 2026-09-30 16:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 16:41</t>
+          <t>更新时间: 2026-09-30 18:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 18:22</t>
+          <t>更新时间: 2026-10-01 10:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 10:33</t>
+          <t>更新时间: 2026-10-01 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 13:44</t>
+          <t>更新时间: 2026-10-01 15:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 15:02</t>
+          <t>更新时间: 2026-10-01 17:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 17:04</t>
+          <t>更新时间: 2026-10-01 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 18:49</t>
+          <t>更新时间: 2026-10-02 10:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 10:44</t>
+          <t>更新时间: 2026-10-02 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 13:28</t>
+          <t>更新时间: 2026-10-02 14:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:51</t>
+          <t>更新时间: 2026-10-02 16:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 16:38</t>
+          <t>更新时间: 2026-10-02 18:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 18:23</t>
+          <t>更新时间: 2026-10-03 10:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:29</t>
+          <t>更新时间: 2026-10-03 13:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:11</t>
+          <t>更新时间: 2026-10-03 14:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 14:15</t>
+          <t>更新时间: 2026-10-03 16:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 16:16</t>
+          <t>更新时间: 2026-10-03 17:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 17:45</t>
+          <t>更新时间: 2026-10-04 11:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 11:04</t>
+          <t>更新时间: 2026-10-04 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 13:45</t>
+          <t>更新时间: 2026-10-04 14:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:41</t>
+          <t>更新时间: 2026-10-04 16:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 16:31</t>
+          <t>更新时间: 2026-10-04 18:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 18:29</t>
+          <t>更新时间: 2026-10-05 10:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 10:34</t>
+          <t>更新时间: 2026-10-05 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 13:30</t>
+          <t>更新时间: 2026-10-05 14:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:43</t>
+          <t>更新时间: 2026-10-05 17:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 17:13</t>
+          <t>更新时间: 2026-10-05 19:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 19:18</t>
+          <t>更新时间: 2026-10-06 11:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 11:27</t>
+          <t>更新时间: 2026-10-06 14:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 14:13</t>
+          <t>更新时间: 2026-10-06 15:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 15:22</t>
+          <t>更新时间: 2026-10-06 17:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 17:06</t>
+          <t>更新时间: 2026-10-06 19:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 19:08</t>
+          <t>更新时间: 2026-10-07 10:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 10:53</t>
+          <t>更新时间: 2026-10-07 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 13:50</t>
+          <t>更新时间: 2026-10-07 15:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 15:02</t>
+          <t>更新时间: 2026-10-07 16:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 16:50</t>
+          <t>更新时间: 2026-10-07 18:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 18:56</t>
+          <t>更新时间: 2026-10-08 11:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 13:55</t>
+          <t>更新时间: 2026-10-08 15:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 15:10</t>
+          <t>更新时间: 2026-10-08 17:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 17:08</t>
+          <t>更新时间: 2026-10-08 19:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 19:14</t>
+          <t>更新时间: 2026-10-09 11:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 11:16</t>
+          <t>更新时间: 2026-10-09 14:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:01</t>
+          <t>更新时间: 2026-10-09 15:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 15:15</t>
+          <t>更新时间: 2026-10-09 17:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 17:15</t>
+          <t>更新时间: 2026-10-09 19:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 19:12</t>
+          <t>更新时间: 2026-10-10 10:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 10:49</t>
+          <t>更新时间: 2026-10-10 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 13:44</t>
+          <t>更新时间: 2026-10-10 14:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:52</t>
+          <t>更新时间: 2026-10-10 16:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 16:38</t>
+          <t>更新时间: 2026-10-10 18:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 18:30</t>
+          <t>更新时间: 2026-10-11 10:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 10:18</t>
+          <t>更新时间: 2026-10-11 13:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 13:39</t>
+          <t>更新时间: 2026-10-11 14:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:56</t>
+          <t>更新时间: 2026-10-11 17:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 17:02</t>
+          <t>更新时间: 2026-10-11 18:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 18:42</t>
+          <t>更新时间: 2026-10-12 10:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 15:09</t>
+          <t>更新时间: 2026-10-12 17:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 17:23</t>
+          <t>更新时间: 2026-10-12 19:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 19:47</t>
+          <t>更新时间: 2026-10-13 11:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 11:59</t>
+          <t>更新时间: 2026-10-13 14:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 17:33</t>
+          <t>更新时间: 2026-10-13 19:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 19:34</t>
+          <t>更新时间: 2026-10-14 10:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 12:46</t>
+          <t>更新时间: 2026-10-14 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:57</t>
+          <t>更新时间: 2026-10-14 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 15:46</t>
+          <t>更新时间: 2026-10-14 17:23</t>
         </is>
       </c>
     </row>
